--- a/buymore_assignment/output.xlsx
+++ b/buymore_assignment/output.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -499,12 +499,16 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Beauty
+Baby</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Face Wash</t>
+          <t>Shampoos
+Men's Grooming
+Face Wash
+Lotions</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -523,30 +527,31 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>RK World Infocom Pvt Ltd, Honasa Consumer Limited</t>
+          <t>Honasa Consumer Limited, RK World Infocom Pvt Ltd</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>- Portal gap: brand verified only on Amazon; not checked/found on Flipkart, Nykaa, Blinkit, Zepto - unverified reach on those channels.
-- Seller risk: 2 third-party seller(s) detected (RK World Infocom Pvt Ltd, Honasa Consumer Limited) - the brand does not fully control the Buy Box.
-- Visibility issue: no sponsored ads detected on Amazon search results - the brand is relying entirely on organic ranking.
-- Listing scored 9/10 but is not maximal - Scored 9/10. Weakest areas: Data Accuracy.</t>
+          <t>- Duplicate listings for the same product ('Mamaearth Onion Shampoo for Hair Growth and Hair Fall Contro') with ASINs B099F3WJKW and B0828PRFKP are competing for the same Buy Box, which can lead to split reviews and sales rank, and the brand should consider merging these listings to consolidate reviews and improve sales.
+- The brand's ad spend is going almost entirely to SKUs that are not the brand's proven bestsellers, as 0 of the 6 sponsored SKUs also appear among the 5 highest-rated listings, which means the hero products are undefended on the brand's own query, and the brand should consider adjusting its ad targeting strategy to prioritize its top-rated products.
+- The listing quality score is 1/10, indicating a significant need for improvement in terms of title words, images, bullets, description, and A+ content, and the brand should prioritize optimizing its listings to improve customer experience and conversion rates.
+- The seller names 'Honasa Consumer Limited' and 'RK World Infocom Pvt Ltd' do not carry the brand name, which may lead to confusion or mistrust among customers, and the brand should consider ensuring that its authorized sellers have consistent and recognizable branding.
+- The lack of key listing elements such as title words, images, bullets, and description may hinder the brand's ability to effectively communicate its product value proposition and differentiate itself from competitors, and the brand should focus on enhancing its listing content to improve visibility and sales.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Biotique</t>
+          <t>Cerave</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -556,7 +561,9 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Moisturizers</t>
+          <t>Moisturizers
+Serums
+Face Wash</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -566,11 +573,11 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/Biotique-Morning-Nectar-Flawless-Lotion/dp/B006NVDWGE
-https://www.amazon.in/Biotique-Cucumber-Tightening-Himalayan-Waters/dp/B00791CS2G
-https://www.amazon.in/Biotique-Papaya-Revitalizing-Removal-Scrub/dp/B004X33GGA
-https://www.amazon.in/Biotique-Protein-Intensive-Regrowth-Treatment/dp/B07YWMQRNJ
-https://www.amazon.in/Biotique-Honey-Refreshing-Foaming-150ml/dp/B00KCLZ6VU</t>
+          <t>https://www.amazon.in/CeraVe-Foaming-Cleanser-Normal-Dermatologist-Developed/dp/B07C5XD33D
+https://www.amazon.in/CeraVe-Acne-Prone-microbeads-Dermatologist-Recommended/dp/B00U1YCRD8
+https://www.amazon.in/CeraVe-Large-Moisturising-Cream-16/dp/B07CHPWFXK
+https://www.amazon.in/CeraVe-Moisturizing-Cream-Very-Skin/dp/B0F59KKYYP
+https://www.amazon.in/CeraVe-Post-Acne-Refining-Resurfacing-Brightening/dp/B07VWSN95S</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -580,7 +587,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -588,204 +595,11 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>- Portal gap: brand verified only on Amazon; not checked/found on Flipkart, Nykaa, Blinkit, Zepto - unverified reach on those channels.
-- Seller risk: 1 third-party seller(s) detected (RK World Infocom Pvt Ltd) - the brand does not fully control the Buy Box.
-- Visibility issue: no sponsored ads detected on Amazon search results - the brand is relying entirely on organic ranking.
-- Seller concentration: only 1 seller found across the sampled listings - a single point of failure for stock and Buy Box control.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Mamaearth</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>- Brand 'Mamaearth' returned no matching listings on Amazon.in - no marketplace presence could be verified.
-- No product URLs, sellers, or rating data available for analysis.
-- No sponsored ad activity observable without a search presence.
-- Listing quality could not be scored (no listing to audit).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Mamaearth</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Beauty</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Face Wash</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/Mamaearth-Natural-Turmeric-Saffron-Removal/dp/B0FPWWH55W
-https://www.amazon.in/Mamaearth-Shampoo-Growth-Control-Keratin/dp/B099F3WJKW
-https://www.amazon.in/Mamaearth-Vitamin-Face-Turmeric-Illumination/dp/B08MF36S6C
-https://www.amazon.in/Mamaearth-Daily-Moisturizing-Lotion-Babies/dp/B0774TQRBZ
-https://www.amazon.in/Mamaearth-Pimple-Control-Salicylic-Acne-Prone/dp/B07FPSB76P</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>RK World Infocom Pvt Ltd, Honasa Consumer Limited</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>- Mamaearth has limited presence on other e-commerce portals such as Flipkart, Nykaa, Blinkit, and Zepto, which could be a weakness in terms of reaching a broader customer base, as evidenced by the list of portals not verified.
-- The brand has only 5 products listed on Amazon, which may not be sufficient to cater to the diverse needs of customers in the face wash category, as per the products found data.
-- Mamaearth relies on only two sellers, RK World Infocom Pvt Ltd and Honasa Consumer Limited, which could be a risk if one of them faces any issues, as seen in the sellers data.
-- The brand's listing quality score is 9/10, but there is room for improvement, particularly in the description section, which is currently missing, as noted in the audit detail.
-- Despite running sponsored ads, Mamaearth may not be fully optimizing its ad spend, as there are only 9 sponsored listings seen, which could be increased to improve visibility and sales.
-- The top product title, while descriptive, is quite long with 27 title words, which may not be fully displayed on all devices, potentially affecting click-through rates, as per the audit detail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Mamaearth</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Beauty
-Baby</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Face Wash
-Shampoos
-Lotions</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/Mamaearth-Natural-Turmeric-Saffron-Removal/dp/B0FPWWH55W
-https://www.amazon.in/Mamaearth-Shampoo-Growth-Control-Keratin/dp/B099F3WJKW
-https://www.amazon.in/Mamaearth-Shampoo-Growth-Control-Keratin/dp/B0828PRFKP
-https://www.amazon.in/Mamaearth-Vitamin-Face-Turmeric-Illumination/dp/B08MF36S6C
-https://www.amazon.in/Mamaearth-Daily-Moisturizing-Lotion-Babies/dp/B0774TQRBZ</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>RK World Infocom Pvt Ltd, Honasa Consumer Limited</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>- Low product diversity: With only 5 products found, Mamaearth's Amazon.in presence lacks variety, which may limit customer choices and drive them to competitors, as seen in the 'Products found: 5' data.
-- Lack of verified presence on other portals: Mamaearth's absence from other major e-commerce platforms like Flipkart, Nykaa, Blinkit, and Zepto, as indicated in 'Portals not verified', may result in missed sales opportunities and reduced brand visibility.
-- Incomplete product listing: The absence of a product description, as noted in 'description=NO', may hinder customers' ability to make informed purchasing decisions, potentially leading to lower conversion rates.
-- Dependence on sponsored ads: With 8 sponsored listings seen, Mamaearth may be relying heavily on paid advertising, which can be costly and unsustainable in the long term, as evidenced by 'Running sponsored ads: Yes'.
-- Vulnerability to seller performance: As Mamaearth's products are sold by third-party sellers like 'RK World Infocom Pvt Ltd', the brand's reputation and customer satisfaction may be impacted by the sellers' performance, highlighting the need for careful seller management.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Mamaearth</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Beauty
-Baby</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Face Wash
-Shampoos
-Lotions</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/Mamaearth-Natural-Turmeric-Saffron-Removal/dp/B0FPWWH55W
-https://www.amazon.in/Mamaearth-Shampoo-Growth-Control-Keratin/dp/B099F3WJKW
-https://www.amazon.in/Mamaearth-Shampoo-Growth-Control-Keratin/dp/B0828PRFKP
-https://www.amazon.in/Mamaearth-Vitamin-Face-Turmeric-Illumination/dp/B08MF36S6C
-https://www.amazon.in/Mamaearth-Daily-Moisturizing-Lotion-Babies/dp/B0774TQRBZ</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>RK World Infocom Pvt Ltd, Honasa Consumer Limited</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>- Duplicate listings exist for the same product, such as Mamaearth Onion Shampoo for Hair Growth and Hair Fall Control, with ASINs B099F3WJKW and B0828PRFKP, which can cause split reviews and sales rank, and should be consolidated to improve customer experience and sales.
-- The brand's seller names, such as RK World Infocom Pvt Ltd and Honasa Consumer Limited, do not carry the brand name, which may lead to confusion among customers and should be standardized to ensure brand consistency.
-- The sampled products span 2 top-level categories, Beauty and Baby, which may indicate a lack of focus on a specific category and should be analyzed to determine the brand's core strengths and weaknesses.
-- The top listing holds 25% of the sampled review volume, with a significant difference in rating counts across listings, ranging from 28,439 to 57,813, which may indicate inconsistent product quality or customer satisfaction and should be investigated to improve overall customer experience.
-- The brand's ad presence is unverified, as no sponsored listings were seen on page one, which may indicate a lack of investment in advertising and should be verified to determine the brand's marketing strategy.</t>
+          <t>- The brand has duplicate listings for the same product ('CeraVe Moisturizing Cream For Dry To Very Dry Skin (454g) - ') with ASINs B07CHPWFXK and B0F59KKYYP, which can cause reviews and sales rank to be split across them and compete for the same Buy Box. Action: Merge or remove duplicate listings to consolidate reviews and sales.
+- Ad spend overlaps with bestsellers, with 4 of the 10 sponsored SKUs also appearing among the 5 highest-rated listings, which may be paying for traffic that would have converted organically. Action: Review ad targeting strategy to optimize ad spend and reduce overlap with organic traffic.
+- The seller name 'RK World Infocom Pvt Ltd' does not carry the brand name, which may indicate a potential issue with authorized distribution or reselling. Action: Investigate and verify the relationship between the seller and the brand to ensure authorized distribution.
+- The listing quality score of 8/10, while strong, indicates some room for improvement. Action: Review and optimize listing elements such as title words, images, bullets, and description to improve the listing quality score.
+- The brand's presence is only confirmed on Amazon.in, with no information available on other portals. Action: Expand presence to other portals such as Flipkart, Nykaa, Blinkit, and Zepto to increase brand visibility and reach.</t>
         </is>
       </c>
     </row>
